--- a/project/HW4/22127410/22127410_GUI_Checklist.xlsx
+++ b/project/HW4/22127410/22127410_GUI_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Documents/Testing-PRJ-SM/project/HW4/22127410/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383D1703-39F6-9D48-B4B7-0B224A69E9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB90463F-F6B2-8F4F-9654-B7C501592F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="157">
   <si>
     <t>ID</t>
   </si>
@@ -491,13 +491,22 @@
   </si>
   <si>
     <t>Vị trí, kích thước của các thành phần trong trang web có hiển thị đúng với các trình duyệt đang được kiểm tra không?</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>All pages</t>
+  </si>
+  <si>
+    <t>This page only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,8 +551,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,6 +577,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -664,9 +687,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -681,9 +702,6 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -694,6 +712,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,7 +734,7 @@
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="GUI name"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GUI detail" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="GUI detail" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Remark"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -721,14 +742,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A4:E80" totalsRowShown="0">
-  <autoFilter ref="A4:E80" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No." dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Checkpoints" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Yes" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="No" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A4:F80" totalsRowShown="0">
+  <autoFilter ref="A4:F80" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No." dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Checkpoints" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Yes" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="No" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Remarks"/>
+    <tableColumn id="6" xr3:uid="{AD9B2A56-CDD0-BE4F-9676-824B51076B0F}" name="Note"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1078,6 +1100,7 @@
     <col min="1" max="1" width="8.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="2" customWidth="1"/>
     <col min="3" max="4" width="6.33203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -1090,6 +1113,7 @@
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
     </row>
     <row r="2" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
@@ -1101,6 +1125,7 @@
       <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
@@ -1110,7 +1135,7 @@
       <c r="C3" s="15"/>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
-      <c r="F3" s="3"/>
+      <c r="F3" s="16"/>
       <c r="H3" s="3"/>
       <c r="I3" s="17"/>
     </row>
@@ -1130,6 +1155,9 @@
       <c r="E4" s="6" t="s">
         <v>117</v>
       </c>
+      <c r="F4" s="6" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18">
@@ -1141,6 +1169,7 @@
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
@@ -1162,6 +1191,9 @@
       <c r="C7" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F7" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
@@ -1173,6 +1205,9 @@
       <c r="C8" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F8" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
@@ -1194,6 +1229,9 @@
       <c r="D10" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F10" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
@@ -1205,6 +1243,9 @@
       <c r="D11" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F11" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
@@ -1216,6 +1257,9 @@
       <c r="D12" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F12" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
@@ -1227,6 +1271,9 @@
       <c r="D13" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F13" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
@@ -1238,6 +1285,9 @@
       <c r="D14" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F14" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
@@ -1249,6 +1299,9 @@
       <c r="D15" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="F15" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
@@ -1260,8 +1313,11 @@
       <c r="D16" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1271,8 +1327,11 @@
       <c r="D17" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1282,8 +1341,11 @@
       <c r="D18" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1293,8 +1355,11 @@
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1304,7 +1369,7 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -1314,8 +1379,11 @@
       <c r="C21" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -1325,8 +1393,11 @@
       <c r="C22" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1336,8 +1407,11 @@
       <c r="C23" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
@@ -1347,8 +1421,11 @@
       <c r="D24" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>98</v>
       </c>
@@ -1358,8 +1435,11 @@
       <c r="C25" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -1369,8 +1449,11 @@
       <c r="C26" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1380,8 +1463,11 @@
       <c r="C27" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
@@ -1391,8 +1477,11 @@
       <c r="D28" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1402,8 +1491,11 @@
       <c r="D29" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1413,8 +1505,11 @@
       <c r="C30" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1424,8 +1519,11 @@
       <c r="C31" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1435,8 +1533,11 @@
       <c r="C32" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1446,8 +1547,11 @@
       <c r="D33" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1457,8 +1561,11 @@
       <c r="D34" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1466,19 +1573,22 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="7" t="s">
         <v>138</v>
       </c>
       <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1488,8 +1598,11 @@
       <c r="C37" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1499,8 +1612,11 @@
       <c r="C38" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1510,8 +1626,11 @@
       <c r="D39" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1521,8 +1640,11 @@
       <c r="D40" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1532,8 +1654,11 @@
       <c r="D41" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1543,8 +1668,11 @@
       <c r="D42" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1554,8 +1682,9 @@
       <c r="C43" s="23"/>
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
-    </row>
-    <row r="44" spans="1:5" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F43" s="26"/>
+    </row>
+    <row r="44" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1565,7 +1694,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>52</v>
       </c>
@@ -1575,8 +1704,11 @@
       <c r="C45" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F45" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1586,8 +1718,11 @@
       <c r="C46" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
@@ -1597,8 +1732,11 @@
       <c r="C47" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F47" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1608,8 +1746,11 @@
       <c r="C48" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1619,8 +1760,11 @@
       <c r="C49" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1630,8 +1774,11 @@
       <c r="C50" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1641,8 +1788,11 @@
       <c r="D51" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1652,7 +1802,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>53</v>
       </c>
@@ -1662,8 +1812,11 @@
       <c r="C53" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>54</v>
       </c>
@@ -1673,8 +1826,11 @@
       <c r="C54" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F54" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -1684,8 +1840,11 @@
       <c r="C55" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F55" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
@@ -1695,8 +1854,11 @@
       <c r="C56" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F56" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -1706,8 +1868,11 @@
       <c r="C57" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F57" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>125</v>
       </c>
@@ -1717,8 +1882,11 @@
       <c r="D58" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F58" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -1728,8 +1896,11 @@
       <c r="C59" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F59" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>127</v>
       </c>
@@ -1739,8 +1910,11 @@
       <c r="D60" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F60" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>128</v>
       </c>
@@ -1750,8 +1924,11 @@
       <c r="D61" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F61" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -1761,8 +1938,11 @@
       <c r="D62" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F62" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -1772,8 +1952,11 @@
       <c r="C63" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F63" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -1783,8 +1966,11 @@
       <c r="D64" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F64" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -1794,7 +1980,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -1804,7 +1990,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -1814,8 +2000,11 @@
       <c r="C67" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F67" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -1825,8 +2014,11 @@
       <c r="D68" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F68" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -1836,8 +2028,11 @@
       <c r="C69" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F69" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -1847,8 +2042,11 @@
       <c r="C70" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="F70" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -1858,8 +2056,11 @@
       <c r="C71" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -1869,7 +2070,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -1879,8 +2080,11 @@
       <c r="C73" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -1890,8 +2094,11 @@
       <c r="C74" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F74" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -1901,7 +2108,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -1911,8 +2118,11 @@
       <c r="C76" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F76" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -1922,8 +2132,11 @@
       <c r="C77" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F77" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -1933,8 +2146,11 @@
       <c r="C78" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F78" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -1944,8 +2160,11 @@
       <c r="C79" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="F79" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>
@@ -1954,6 +2173,9 @@
       </c>
       <c r="C80" s="7" t="s">
         <v>138</v>
+      </c>
+      <c r="F80" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
